--- a/public/templates/import-analysis-type-elements.xlsx
+++ b/public/templates/import-analysis-type-elements.xlsx
@@ -10,12 +10,12 @@
     <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
   <si>
     <t>parameter</t>
   </si>
@@ -39,6 +39,12 @@
   </si>
   <si>
     <t>equipment</t>
+  </si>
+  <si>
+    <t>lod</t>
+  </si>
+  <si>
+    <t>loq</t>
   </si>
   <si>
     <t>pH</t>
@@ -79,7 +85,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -89,13 +95,28 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -110,8 +131,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,83 +435,112 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="19.852" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="15.139" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="6.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="6.998" bestFit="true" customWidth="true" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>0.01</v>
+      </c>
+      <c r="J2">
+        <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3"/>
+        <v>19</v>
+      </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>0.001</v>
+      </c>
+      <c r="J3">
+        <v>0.005</v>
       </c>
     </row>
   </sheetData>
